--- a/INDEX/INDEX_261029_v2.xlsx
+++ b/INDEX/INDEX_261029_v2.xlsx
@@ -12625,12 +12625,12 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>유니씨앤씨</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>카탈로그_유니</t>
         </is>
       </c>
     </row>
